--- a/converted/oylik/2026-08/Elektr Fiderlar.xlsx
+++ b/converted/oylik/2026-08/Elektr Fiderlar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="148">
   <si>
     <t>Fiderlar Avgust Holatiga Ko'ra</t>
   </si>
@@ -46,6 +46,15 @@
     <t>Fider Nomi (manba)</t>
   </si>
   <si>
+    <t>Umumiy oqim (fider faylida)</t>
+  </si>
+  <si>
+    <t>Foydali oqim (fider faylida)</t>
+  </si>
+  <si>
+    <t>Yo’qotish (fider faylida)</t>
+  </si>
+  <si>
     <t>Manzil (manba)</t>
   </si>
   <si>
@@ -55,6 +64,9 @@
     <t>Ma'sul xodim (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
@@ -115,6 +127,9 @@
     <t xml:space="preserve">Ziyokor </t>
   </si>
   <si>
+    <t>Shu oyda TP oqimlari yo'q - oqim fider faylida qolgan (TP lari yig'indisi 0)</t>
+  </si>
+  <si>
     <t>baliqchi/Avgust/Elektr Fiderlar.xlsx, 6-qator</t>
   </si>
   <si>
@@ -133,6 +148,93 @@
     <t>baliqchi/Avgust/Elektr Fiderlar.xlsx, 8-qator</t>
   </si>
   <si>
+    <t>Baliqchi</t>
+  </si>
+  <si>
+    <t>Oqtom</t>
+  </si>
+  <si>
+    <t>Eski Markaz MFY</t>
+  </si>
+  <si>
+    <t>Sh.Xojimatov</t>
+  </si>
+  <si>
+    <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 9-qator</t>
+  </si>
+  <si>
+    <t>Sifat savdo</t>
+  </si>
+  <si>
+    <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 10-qator</t>
+  </si>
+  <si>
+    <t>FNM ist</t>
+  </si>
+  <si>
+    <t>Avgust faylida yo'q - oqim 0 (nomi va boshqa ma'lumotlari baliqchi/7 oylik/Elektr Fiderlar.xlsx dan)</t>
+  </si>
+  <si>
+    <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 11-qator</t>
+  </si>
+  <si>
+    <t>Farovon</t>
+  </si>
+  <si>
+    <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 12-qator</t>
+  </si>
+  <si>
+    <t>Navbahor</t>
+  </si>
+  <si>
+    <t>Yakkatol MFY, Olchazor MFY</t>
+  </si>
+  <si>
+    <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 13-qator</t>
+  </si>
+  <si>
+    <t>Oybuloq</t>
+  </si>
+  <si>
+    <t>Barkamol MFY, Turkiston MFY, Jasorat MFY, Sortepa MFY</t>
+  </si>
+  <si>
+    <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 14-qator</t>
+  </si>
+  <si>
+    <t>Go'ravon</t>
+  </si>
+  <si>
+    <t>Go'ravon MFY, O'rtaqo'rg'on MFY, Serquyosh MFY</t>
+  </si>
+  <si>
+    <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 15-qator</t>
+  </si>
+  <si>
+    <t>Oqqo'rg'on</t>
+  </si>
+  <si>
+    <t>Markaz MFY, Islomobod MFY, Oqqo'rg'on MFY</t>
+  </si>
+  <si>
+    <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 16-qator</t>
+  </si>
+  <si>
+    <t>Sarkor</t>
+  </si>
+  <si>
+    <t>Eski Markaz MFY, Turkiston MFY, Ko'l bo'yi MFY</t>
+  </si>
+  <si>
+    <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 17-qator</t>
+  </si>
+  <si>
+    <t>Sortepa MFY</t>
+  </si>
+  <si>
+    <t>baliqchi/7 oylik/Elektr Fiderlar.xlsx, 18-qator</t>
+  </si>
+  <si>
     <t>Chinobod</t>
   </si>
   <si>
@@ -160,6 +262,9 @@
     <t>С.Мирзахакимов</t>
   </si>
   <si>
+    <t>Quvvati (KVA) o'rnida kuchlanish (kV) yozilgan - bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>chinobod/Elektr Fiderlar.xlsx [Avgust], 3-qator</t>
   </si>
   <si>
@@ -205,6 +310,9 @@
     <t>Фаровон МФЙ</t>
   </si>
   <si>
+    <t>Quvvati (KVA) o'rnida kuchlanish (kV) yozilgan - bo'sh qoldirildi; Shu oyda TP oqimlari yo'q - oqim fider faylida qolgan (TP lari yig'indisi 0)</t>
+  </si>
+  <si>
     <t>chinobod/Elektr Fiderlar.xlsx [Avgust], 6-qator</t>
   </si>
   <si>
@@ -302,6 +410,51 @@
   </si>
   <si>
     <t>chinobod/Elektr Fiderlar.xlsx [Avgust], 12-qator</t>
+  </si>
+  <si>
+    <t>Sevin TIM</t>
+  </si>
+  <si>
+    <t>baliqchi_transformatorlar.xlsx [Avgust], 369-qator</t>
+  </si>
+  <si>
+    <t>Oltinko'l</t>
+  </si>
+  <si>
+    <t>Alpomish</t>
+  </si>
+  <si>
+    <t>transformatorlar.xlsx [Avgust], 41-qator</t>
+  </si>
+  <si>
+    <t>Muqum</t>
+  </si>
+  <si>
+    <t>Fiderlar faylida yo'q, faqat reestr yoki quyi fayllarda bor - oqim 0</t>
+  </si>
+  <si>
+    <t>baliqchi/Elektr Abonentlar.xlsx, 6583-qator</t>
+  </si>
+  <si>
+    <t>Olimbek</t>
+  </si>
+  <si>
+    <t>baliqchi/Elektr Abonentlar.xlsx, 10175-qator</t>
+  </si>
+  <si>
+    <t>Biriktirilmagan</t>
+  </si>
+  <si>
+    <t>Vaqtinchalik "Biriktirilmagan" fider - abonentlarning joyi hali berilmagan</t>
+  </si>
+  <si>
+    <t>chinobod/Elektr Abonentlar.xlsx, 73-qator</t>
+  </si>
+  <si>
+    <t>Bo'zchi</t>
+  </si>
+  <si>
+    <t>chinobod/Elektr Abonentlar.xlsx, 118-qator</t>
   </si>
 </sst>
 </file>
@@ -716,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
@@ -724,10 +877,10 @@
     <col min="6" max="6" width="34" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="14" width="26" customWidth="1"/>
+    <col min="9" max="18" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -744,8 +897,12 @@
       <c r="L1"/>
       <c r="M1"/>
       <c r="N1"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1"/>
+      <c r="P1"/>
+      <c r="Q1"/>
+      <c r="R1"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -788,112 +945,151 @@
       <c r="N2" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1">
+        <v>557578.645402</v>
+      </c>
+      <c r="D3" s="1">
+        <v>478747.82481</v>
+      </c>
+      <c r="E3" s="1">
+        <v>78830.820592</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3">
         <v>262272</v>
       </c>
-      <c r="D3" s="1">
+      <c r="L3">
         <v>231646</v>
       </c>
-      <c r="E3" s="1">
+      <c r="M3">
         <v>34625</v>
       </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="1">
+        <v>385132.466255</v>
+      </c>
+      <c r="D4" s="1">
+        <v>331814.612399</v>
+      </c>
+      <c r="E4" s="1">
+        <v>53317.853856</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="I4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="1">
+      <c r="K4">
         <v>184014</v>
       </c>
-      <c r="D4" s="1">
+      <c r="L4">
         <v>161102</v>
       </c>
-      <c r="E4" s="1">
+      <c r="M4">
         <v>22912</v>
       </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C5" s="1">
+        <v>687598.968103</v>
+      </c>
+      <c r="D5" s="1">
+        <v>583049.607715</v>
+      </c>
+      <c r="E5" s="1">
+        <v>104549.360389</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5">
         <v>257860</v>
       </c>
-      <c r="D5" s="1">
+      <c r="L5">
         <v>219618</v>
       </c>
-      <c r="E5" s="1">
+      <c r="M5">
         <v>38241</v>
       </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1">
         <v>3075.46</v>
@@ -905,27 +1101,30 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1">
         <v>344.91</v>
@@ -937,27 +1136,30 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" t="s">
         <v>19</v>
       </c>
-      <c r="K7" t="s">
-        <v>15</v>
-      </c>
-      <c r="N7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
@@ -969,434 +1171,1024 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" t="s">
         <v>19</v>
       </c>
-      <c r="K8" t="s">
-        <v>15</v>
-      </c>
-      <c r="N8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="R8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1">
-        <v>232000</v>
+        <v>11018.955592</v>
       </c>
       <c r="D9" s="1">
-        <v>194880</v>
+        <v>9318.748916</v>
       </c>
       <c r="E9" s="1">
-        <v>37120</v>
+        <v>1700.206677</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>45</v>
-      </c>
-      <c r="K9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M9" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>40</v>
       </c>
       <c r="B10" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="1">
+        <v>72438.955592</v>
+      </c>
+      <c r="D10" s="1">
+        <v>70738.748916</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1700.206677</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="1">
+        <v>11018.955592</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9318.748916</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1700.206677</v>
+      </c>
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="1">
+        <v>941194.888957</v>
+      </c>
+      <c r="D13" s="1">
+        <v>817789.868304</v>
+      </c>
+      <c r="E13" s="1">
+        <v>123405.020652</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="R13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1749649.478245</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1489672.322851</v>
+      </c>
+      <c r="E14" s="1">
+        <v>259977.155394</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="1">
+        <v>615893.957582</v>
+      </c>
+      <c r="D15" s="1">
+        <v>513677.470367</v>
+      </c>
+      <c r="E15" s="1">
+        <v>102216.487215</v>
+      </c>
+      <c r="F15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="R15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2086800.272283</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1835718.516272</v>
+      </c>
+      <c r="E16" s="1">
+        <v>251081.756011</v>
+      </c>
+      <c r="F16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="R16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1930300.500804</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1711138.76862</v>
+      </c>
+      <c r="E17" s="1">
+        <v>219161.732185</v>
+      </c>
+      <c r="F17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="R17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>53</v>
+      </c>
+      <c r="R18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="1">
+        <v>365289.414213</v>
+      </c>
+      <c r="D19" s="1">
+        <v>304538.818892</v>
+      </c>
+      <c r="E19" s="1">
+        <v>60750.595321</v>
+      </c>
+      <c r="F19" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" t="s">
+        <v>78</v>
+      </c>
+      <c r="J19" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19">
+        <v>232000</v>
+      </c>
+      <c r="L19">
+        <v>194880</v>
+      </c>
+      <c r="M19">
+        <v>37120</v>
+      </c>
+      <c r="N19" t="s">
+        <v>80</v>
+      </c>
+      <c r="O19" t="s">
+        <v>81</v>
+      </c>
+      <c r="P19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>83</v>
+      </c>
+      <c r="R19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1301709.249397</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1083285.612327</v>
+      </c>
+      <c r="E20" s="1">
+        <v>218423.63707</v>
+      </c>
+      <c r="F20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" t="s">
+        <v>78</v>
+      </c>
+      <c r="J20" t="s">
+        <v>87</v>
+      </c>
+      <c r="K20">
         <v>548000</v>
       </c>
-      <c r="D10" s="1">
+      <c r="L20">
         <v>460320</v>
       </c>
-      <c r="E10" s="1">
+      <c r="M20">
         <v>87680</v>
       </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" t="s">
-        <v>52</v>
-      </c>
-      <c r="K10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="N20" t="s">
+        <v>88</v>
+      </c>
+      <c r="O20" t="s">
+        <v>81</v>
+      </c>
+      <c r="P20" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>83</v>
+      </c>
+      <c r="R20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1259689.903686</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1055784.550828</v>
+      </c>
+      <c r="E21" s="1">
+        <v>203905.352858</v>
+      </c>
+      <c r="F21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s">
+        <v>92</v>
+      </c>
+      <c r="K21">
         <v>1344000</v>
       </c>
-      <c r="D11" s="1">
+      <c r="L21">
         <v>1128960</v>
       </c>
-      <c r="E11" s="1">
+      <c r="M21">
         <v>215040</v>
       </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K11" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="N21" t="s">
+        <v>93</v>
+      </c>
+      <c r="O21" t="s">
+        <v>81</v>
+      </c>
+      <c r="P21" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>83</v>
+      </c>
+      <c r="R21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="1">
         <v>204000</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D22" s="1">
         <v>171360</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E22" s="1">
         <v>32640</v>
       </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" t="s">
-        <v>62</v>
-      </c>
-      <c r="K12" t="s">
-        <v>63</v>
-      </c>
-      <c r="L12" t="s">
-        <v>47</v>
-      </c>
-      <c r="M12" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="F22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J22" t="s">
+        <v>97</v>
+      </c>
+      <c r="N22" t="s">
+        <v>98</v>
+      </c>
+      <c r="O22" t="s">
+        <v>81</v>
+      </c>
+      <c r="P22" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>99</v>
+      </c>
+      <c r="R22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="1">
+        <v>467663.266244</v>
+      </c>
+      <c r="D23" s="1">
+        <v>389474.013435</v>
+      </c>
+      <c r="E23" s="1">
+        <v>78189.252809</v>
+      </c>
+      <c r="F23" t="s">
+        <v>102</v>
+      </c>
+      <c r="H23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23" t="s">
+        <v>103</v>
+      </c>
+      <c r="K23">
         <v>196000</v>
       </c>
-      <c r="D13" s="1">
+      <c r="L23">
         <v>164640</v>
       </c>
-      <c r="E13" s="1">
+      <c r="M23">
         <v>31360</v>
       </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" t="s">
-        <v>47</v>
-      </c>
-      <c r="M13" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="N23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O23" t="s">
+        <v>81</v>
+      </c>
+      <c r="P23" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>83</v>
+      </c>
+      <c r="R23" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="1">
+        <v>889526.921015</v>
+      </c>
+      <c r="D24" s="1">
+        <v>738878.375537</v>
+      </c>
+      <c r="E24" s="1">
+        <v>150648.545478</v>
+      </c>
+      <c r="F24" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s">
+        <v>78</v>
+      </c>
+      <c r="J24" t="s">
+        <v>108</v>
+      </c>
+      <c r="K24">
         <v>447000</v>
       </c>
-      <c r="D14" s="1">
+      <c r="L24">
         <v>375480</v>
       </c>
-      <c r="E14" s="1">
+      <c r="M24">
         <v>71520</v>
       </c>
-      <c r="F14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" t="s">
-        <v>72</v>
-      </c>
-      <c r="K14" t="s">
-        <v>73</v>
-      </c>
-      <c r="L14" t="s">
-        <v>47</v>
-      </c>
-      <c r="M14" t="s">
-        <v>48</v>
-      </c>
-      <c r="N14" t="s">
+      <c r="N24" t="s">
+        <v>109</v>
+      </c>
+      <c r="O24" t="s">
+        <v>81</v>
+      </c>
+      <c r="P24" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>83</v>
+      </c>
+      <c r="R24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="B25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="1">
         <v>272000</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D25" s="1">
         <v>228480</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E25" s="1">
         <v>43520</v>
       </c>
-      <c r="F15" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" t="s">
-        <v>44</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="F25" t="s">
+        <v>112</v>
+      </c>
+      <c r="H25" t="s">
         <v>77</v>
       </c>
-      <c r="K15" t="s">
+      <c r="I25" t="s">
         <v>78</v>
       </c>
-      <c r="L15" t="s">
-        <v>47</v>
-      </c>
-      <c r="M15" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="J25" t="s">
+        <v>113</v>
+      </c>
+      <c r="N25" t="s">
+        <v>114</v>
+      </c>
+      <c r="O25" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="1">
+      <c r="P25" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>99</v>
+      </c>
+      <c r="R25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1149056.068998</v>
+      </c>
+      <c r="D26" s="1">
+        <v>953203.750348</v>
+      </c>
+      <c r="E26" s="1">
+        <v>195852.31865</v>
+      </c>
+      <c r="F26" t="s">
+        <v>118</v>
+      </c>
+      <c r="H26" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s">
+        <v>119</v>
+      </c>
+      <c r="J26" t="s">
+        <v>120</v>
+      </c>
+      <c r="K26">
         <v>786000</v>
       </c>
-      <c r="D16" s="1">
+      <c r="L26">
         <v>660240</v>
       </c>
-      <c r="E16" s="1">
+      <c r="M26">
         <v>125760</v>
       </c>
-      <c r="F16" t="s">
+      <c r="N26" t="s">
+        <v>121</v>
+      </c>
+      <c r="O26" t="s">
+        <v>81</v>
+      </c>
+      <c r="P26" t="s">
         <v>82</v>
       </c>
-      <c r="H16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="Q26" t="s">
         <v>83</v>
       </c>
-      <c r="J16" t="s">
-        <v>84</v>
-      </c>
-      <c r="K16" t="s">
-        <v>85</v>
-      </c>
-      <c r="L16" t="s">
-        <v>47</v>
-      </c>
-      <c r="M16" t="s">
-        <v>48</v>
-      </c>
-      <c r="N16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="R26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="1">
+        <v>889648.085045</v>
+      </c>
+      <c r="D27" s="1">
+        <v>737826.721975</v>
+      </c>
+      <c r="E27" s="1">
+        <v>151821.36307</v>
+      </c>
+      <c r="F27" t="s">
+        <v>124</v>
+      </c>
+      <c r="H27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" t="s">
+        <v>119</v>
+      </c>
+      <c r="J27" t="s">
+        <v>125</v>
+      </c>
+      <c r="K27">
         <v>1080000</v>
       </c>
-      <c r="D17" s="1">
+      <c r="L27">
         <v>907200</v>
       </c>
-      <c r="E17" s="1">
+      <c r="M27">
         <v>172800</v>
       </c>
-      <c r="F17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="N27" t="s">
+        <v>126</v>
+      </c>
+      <c r="O27" t="s">
+        <v>81</v>
+      </c>
+      <c r="P27" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q27" t="s">
         <v>83</v>
       </c>
-      <c r="J17" t="s">
-        <v>89</v>
-      </c>
-      <c r="K17" t="s">
-        <v>90</v>
-      </c>
-      <c r="L17" t="s">
-        <v>47</v>
-      </c>
-      <c r="M17" t="s">
-        <v>48</v>
-      </c>
-      <c r="N17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="1">
+      <c r="R27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1008606.336704</v>
+      </c>
+      <c r="D28" s="1">
+        <v>837271.547391</v>
+      </c>
+      <c r="E28" s="1">
+        <v>171334.789314</v>
+      </c>
+      <c r="F28" t="s">
+        <v>129</v>
+      </c>
+      <c r="H28" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" t="s">
+        <v>119</v>
+      </c>
+      <c r="J28" t="s">
+        <v>130</v>
+      </c>
+      <c r="K28">
         <v>780000</v>
       </c>
-      <c r="D18" s="1">
+      <c r="L28">
         <v>655200</v>
       </c>
-      <c r="E18" s="1">
+      <c r="M28">
         <v>124800</v>
       </c>
-      <c r="F18" t="s">
-        <v>93</v>
-      </c>
-      <c r="H18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="N28" t="s">
+        <v>131</v>
+      </c>
+      <c r="O28" t="s">
+        <v>81</v>
+      </c>
+      <c r="P28" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q28" t="s">
         <v>83</v>
       </c>
-      <c r="J18" t="s">
-        <v>94</v>
-      </c>
-      <c r="K18" t="s">
-        <v>95</v>
-      </c>
-      <c r="L18" t="s">
-        <v>47</v>
-      </c>
-      <c r="M18" t="s">
-        <v>48</v>
-      </c>
-      <c r="N18" t="s">
-        <v>96</v>
+      <c r="R28" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="1">
+        <v>11018.955592</v>
+      </c>
+      <c r="D29" s="1">
+        <v>9318.748916</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1700.206677</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="R29" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="1">
+        <v>656814.754698</v>
+      </c>
+      <c r="D30" s="1">
+        <v>545699.609268</v>
+      </c>
+      <c r="E30" s="1">
+        <v>111115.145431</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="R30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>139</v>
+      </c>
+      <c r="R31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="1">
+        <v>0</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>139</v>
+      </c>
+      <c r="R32" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>144</v>
+      </c>
+      <c r="R33" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>139</v>
+      </c>
+      <c r="R34" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
